--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\AO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\AO\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Maqaa</t>
   </si>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t xml:space="preserve">Fayyisaa Badhuu </t>
-  </si>
-  <si>
-    <t>Salamoon Zarihuun</t>
   </si>
   <si>
     <t>Qananiisaa Biqilaa</t>
@@ -381,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
@@ -419,7 +416,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1">
         <v>913354650</v>
@@ -433,7 +430,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1">
         <v>917372534</v>
@@ -447,7 +444,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1">
         <v>912695064</v>
@@ -464,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>926757080</v>
+        <v>911818685</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -478,7 +475,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>911818685</v>
+        <v>913216895</v>
       </c>
       <c r="C7">
         <v>10000</v>
@@ -489,29 +486,15 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>913216895</v>
+        <v>985816078</v>
       </c>
       <c r="C8">
         <v>10000</v>
       </c>
       <c r="D8">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1">
-        <v>985816078</v>
-      </c>
-      <c r="C9">
-        <v>10000</v>
-      </c>
-      <c r="D9">
         <v>100000</v>
       </c>
     </row>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Maqaa</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Dajanee Guutaa</t>
-  </si>
-  <si>
-    <t>Abarraa Asaffaa</t>
   </si>
   <si>
     <t>Girmaa Masqalaa fi Lammii Diroo</t>
@@ -378,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
@@ -416,7 +413,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1">
         <v>913354650</v>
@@ -430,10 +427,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1">
-        <v>917372534</v>
+        <v>912695064</v>
       </c>
       <c r="C4">
         <v>10000</v>
@@ -444,10 +441,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>912695064</v>
+        <v>911818685</v>
       </c>
       <c r="C5">
         <v>10000</v>
@@ -458,10 +455,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>911818685</v>
+        <v>913216895</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -472,29 +469,15 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>913216895</v>
+        <v>985816078</v>
       </c>
       <c r="C7">
         <v>10000</v>
       </c>
       <c r="D7">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1">
-        <v>985816078</v>
-      </c>
-      <c r="C8">
-        <v>10000</v>
-      </c>
-      <c r="D8">
         <v>100000</v>
       </c>
     </row>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Maqaa</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Jabeessaa Caalaa fi Getuu Baqqalaa</t>
-  </si>
-  <si>
-    <t>Warqii Lammaa fi Silashii Dhabasaa</t>
   </si>
 </sst>
 </file>
@@ -375,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
@@ -467,20 +464,6 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1">
-        <v>985816078</v>
-      </c>
-      <c r="C7">
-        <v>10000</v>
-      </c>
-      <c r="D7">
-        <v>100000</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/AO_uqubii.xlsx
+++ b/AO_uqubii.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Maqaa</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Dajanee Guutaa</t>
-  </si>
-  <si>
-    <t>Girmaa Masqalaa fi Lammii Diroo</t>
   </si>
   <si>
     <t>Jabeessaa Caalaa fi Getuu Baqqalaa</t>
@@ -372,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
@@ -413,7 +410,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1">
-        <v>913354650</v>
+        <v>912695064</v>
       </c>
       <c r="C3">
         <v>10000</v>
@@ -424,10 +421,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>912695064</v>
+        <v>911818685</v>
       </c>
       <c r="C4">
         <v>10000</v>
@@ -438,29 +435,15 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>911818685</v>
+        <v>913216895</v>
       </c>
       <c r="C5">
         <v>10000</v>
       </c>
       <c r="D5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
-        <v>913216895</v>
-      </c>
-      <c r="C6">
-        <v>10000</v>
-      </c>
-      <c r="D6">
         <v>100000</v>
       </c>
     </row>
